--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -389,7 +389,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ServiceRequest.meta.versionId</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-servicerequest-common.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>
